--- a/p6_deployment/data/italy/missing/data_understanding/all/df_match_miss.xlsx
+++ b/p6_deployment/data/italy/missing/data_understanding/all/df_match_miss.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>EJLKYOz</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>tjY4uUe</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>MLVBCoY</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>xjigzK8</t>
+          <t>xjigzK81</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>n10g3Kf</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>A1CicVE</t>
+          <t>A1CicVEU</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Qu12kvX</t>
+          <t>Qu12kvXf</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>AcgUMf0</t>
+          <t>AcgUMf0E</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>S8Ygn9M</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>j32a3mq</t>
+          <t>j32a3mqs</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>EJLKYOz</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>4IdjsvY</t>
+          <t>4IdjsvY2</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>MVSS7qF</t>
+          <t>MVSS7qFe</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>KtGrCa5</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>A72TGDl</t>
+          <t>A72TGDlt</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>rTrn0h4</t>
+          <t>rTrn0h4a</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
@@ -3292,7 +3292,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>tYVGfTo</t>
+          <t>tYVGfTo2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>619UPLr</t>
+          <t>619UPLrb</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>tSiEeKv</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>bBhpZV2</t>
+          <t>bBhpZV2s</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>zFLwLRZ</t>
+          <t>zFLwLRZS</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>tjY4uUe</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>bBhpZV2</t>
+          <t>bBhpZV2s</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>tYVGfTo</t>
+          <t>tYVGfTo2</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>rTrn0h4</t>
+          <t>rTrn0h4a</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>S8Ygn9M</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>xjigzK8</t>
+          <t>xjigzK81</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>tSiEeKv</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>j32a3mq</t>
+          <t>j32a3mqs</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>Qu12kvX</t>
+          <t>Qu12kvXf</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>619UPLr</t>
+          <t>619UPLrb</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>n10g3Kf</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>A1CicVE</t>
+          <t>A1CicVEU</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>MLVBCoY</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>AcgUMf0</t>
+          <t>AcgUMf0E</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>zFLwLRZ</t>
+          <t>zFLwLRZS</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>4IdjsvY</t>
+          <t>4IdjsvY2</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>A72TGDl</t>
+          <t>A72TGDlt</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>KtGrCa5</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>ryme5Xs</t>
+          <t>ryme5Xs1</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>tjY4uUe</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>MVSS7qF</t>
+          <t>MVSS7qFe</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>tjY4uUe</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>619UPLr</t>
+          <t>619UPLrb</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>KtGrCa5</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>A1CicVE</t>
+          <t>A1CicVEU</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>EJLKYOz</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>xjigzK8</t>
+          <t>xjigzK81</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
@@ -7956,7 +7956,7 @@
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>lUkw2EZ</t>
+          <t>lUkw2EZn</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>rTrn0h4</t>
+          <t>rTrn0h4a</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>tSiEeKv</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>AcgUMf0</t>
+          <t>AcgUMf0E</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>S8Ygn9M</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>4IdjsvY</t>
+          <t>4IdjsvY2</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>Qu12kvX</t>
+          <t>Qu12kvXf</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>MLVBCoY</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>A72TGDl</t>
+          <t>A72TGDlt</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>zFLwLRZ</t>
+          <t>zFLwLRZS</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>MVSS7qF</t>
+          <t>MVSS7qFe</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
@@ -9424,7 +9424,7 @@
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>bBhpZV2</t>
+          <t>bBhpZV2s</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>n10g3Kf</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
@@ -9706,7 +9706,7 @@
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>j32a3mq</t>
+          <t>j32a3mqs</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>A1CicVE</t>
+          <t>A1CicVEU</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
@@ -9988,7 +9988,7 @@
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>MVSS7qF</t>
+          <t>MVSS7qFe</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>rTrn0h4</t>
+          <t>rTrn0h4a</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
@@ -10278,7 +10278,7 @@
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>EJLKYOz</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
@@ -10558,7 +10558,7 @@
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>xjigzK8</t>
+          <t>xjigzK81</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>lUkw2EZ</t>
+          <t>lUkw2EZn</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
@@ -10848,7 +10848,7 @@
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>A72TGDl</t>
+          <t>A72TGDlt</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>tSiEeKv</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
@@ -11138,7 +11138,7 @@
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>MLVBCoY</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>n10g3Kf</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>S8Ygn9M</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>tjY4uUe</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
@@ -11718,7 +11718,7 @@
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>zFLwLRZ</t>
+          <t>zFLwLRZS</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
@@ -11728,7 +11728,7 @@
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>KtGrCa5</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
@@ -12016,7 +12016,7 @@
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>AcgUMf0</t>
+          <t>AcgUMf0E</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
@@ -12026,7 +12026,7 @@
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>j32a3mq</t>
+          <t>j32a3mqs</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
@@ -12306,7 +12306,7 @@
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>619UPLr</t>
+          <t>619UPLrb</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
@@ -12316,7 +12316,7 @@
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>Qu12kvX</t>
+          <t>Qu12kvXf</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
@@ -12596,7 +12596,7 @@
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>4IdjsvY</t>
+          <t>4IdjsvY2</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>bBhpZV2</t>
+          <t>bBhpZV2s</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
@@ -12886,7 +12886,7 @@
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>tSiEeKv</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
@@ -12896,7 +12896,7 @@
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>zFLwLRZ</t>
+          <t>zFLwLRZS</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>tjY4uUe</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
@@ -13186,7 +13186,7 @@
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>AcgUMf0</t>
+          <t>AcgUMf0E</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>EJLKYOz</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
@@ -13476,7 +13476,7 @@
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>MLVBCoY</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>MVSS7qF</t>
+          <t>MVSS7qFe</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
@@ -13766,7 +13766,7 @@
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>xjigzK8</t>
+          <t>xjigzK81</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
@@ -14046,7 +14046,7 @@
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>bBhpZV2</t>
+          <t>bBhpZV2s</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
@@ -14056,7 +14056,7 @@
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>A1CicVE</t>
+          <t>A1CicVEU</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
@@ -14336,7 +14336,7 @@
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>j32a3mq</t>
+          <t>j32a3mqs</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>4IdjsvY</t>
+          <t>4IdjsvY2</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
@@ -14634,7 +14634,7 @@
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>Qu12kvX</t>
+          <t>Qu12kvXf</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>S8Ygn9M</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>lUkw2EZ</t>
+          <t>lUkw2EZn</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
@@ -14934,7 +14934,7 @@
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>A72TGDl</t>
+          <t>A72TGDlt</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
@@ -15214,7 +15214,7 @@
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>KtGrCa5</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
@@ -15224,7 +15224,7 @@
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>619UPLr</t>
+          <t>619UPLrb</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>n10g3Kf</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
@@ -15514,7 +15514,7 @@
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>rTrn0h4</t>
+          <t>rTrn0h4a</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
@@ -15778,7 +15778,7 @@
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>A1CicVE</t>
+          <t>A1CicVEU</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
@@ -15788,7 +15788,7 @@
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>xjigzK8</t>
+          <t>xjigzK81</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
@@ -16068,7 +16068,7 @@
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>A72TGDl</t>
+          <t>A72TGDlt</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
@@ -16078,7 +16078,7 @@
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>j32a3mq</t>
+          <t>j32a3mqs</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
@@ -16366,7 +16366,7 @@
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>xjigzK8</t>
+          <t>xjigzK81</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
@@ -16376,7 +16376,7 @@
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>bBhpZV2</t>
+          <t>bBhpZV2s</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
@@ -16648,7 +16648,7 @@
       <c r="AX56" t="inlineStr"/>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>619UPLr</t>
+          <t>619UPLrb</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
@@ -16658,7 +16658,7 @@
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>EJLKYOz</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
@@ -16938,7 +16938,7 @@
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>rTrn0h4</t>
+          <t>rTrn0h4a</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
@@ -16948,7 +16948,7 @@
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>tjY4uUe</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
@@ -17228,7 +17228,7 @@
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>KdJpmvQ</t>
+          <t>KdJpmvQM</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
@@ -17238,7 +17238,7 @@
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>n10g3Kf</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
@@ -17518,7 +17518,7 @@
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>AcgUMf0</t>
+          <t>AcgUMf0E</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
@@ -17528,7 +17528,7 @@
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>KtGrCa5</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
@@ -17808,7 +17808,7 @@
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>S8Ygn9M</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
@@ -17818,7 +17818,7 @@
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>EDkXRoL</t>
+          <t>EDkXRoLT</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
@@ -18098,7 +18098,7 @@
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>MLVBCoY</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
@@ -18108,7 +18108,7 @@
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>MVSS7qF</t>
+          <t>MVSS7qFe</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
@@ -18388,7 +18388,7 @@
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>zFLwLRZ</t>
+          <t>zFLwLRZS</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
@@ -18398,7 +18398,7 @@
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>lUkw2EZ</t>
+          <t>lUkw2EZn</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
@@ -18678,7 +18678,7 @@
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>tSiEeKv</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
@@ -18688,7 +18688,7 @@
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>Qu12kvX</t>
+          <t>Qu12kvXf</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
@@ -18968,7 +18968,7 @@
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>EJLKYOz</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
@@ -18978,7 +18978,7 @@
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>S8Ygn9M</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
@@ -19258,7 +19258,7 @@
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>tjY4uUe</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
@@ -19268,7 +19268,7 @@
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>tSiEeKv</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
@@ -19304,7 +19304,12 @@
           <t>14.04.2024 15:45</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Fourneau F.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
           <t>Stadio Giuseppe Meazza (San Siro)
@@ -19543,7 +19548,7 @@
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>j32a3mq</t>
+          <t>j32a3mqs</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
@@ -19553,7 +19558,7 @@
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>zFLwLRZ</t>
+          <t>zFLwLRZS</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
@@ -19833,7 +19838,7 @@
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>AcgUMf0</t>
+          <t>AcgUMf0E</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
@@ -19843,7 +19848,7 @@
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>A72TGDl</t>
+          <t>A72TGDlt</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
@@ -20123,7 +20128,7 @@
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>MVSS7qF</t>
+          <t>MVSS7qFe</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
@@ -20133,7 +20138,7 @@
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>n10g3Kf</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
@@ -20421,7 +20426,7 @@
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>bBhpZV2</t>
+          <t>bBhpZV2s</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
@@ -20431,7 +20436,7 @@
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>619UPLr</t>
+          <t>619UPLrb</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
@@ -20711,7 +20716,7 @@
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>4IdjsvY</t>
+          <t>4IdjsvY2</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
@@ -20721,7 +20726,7 @@
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>lUkw2EZ</t>
+          <t>lUkw2EZn</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
@@ -21009,7 +21014,7 @@
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>KtGrCa5</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
@@ -21019,7 +21024,7 @@
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>MLVBCoY</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
@@ -21299,7 +21304,7 @@
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>Qu12kvX</t>
+          <t>Qu12kvXf</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
@@ -21309,7 +21314,7 @@
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>rTrn0h4</t>
+          <t>rTrn0h4a</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
@@ -21589,7 +21594,7 @@
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>EDkXRoL</t>
+          <t>EDkXRoLT</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
@@ -21599,7 +21604,7 @@
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>j32a3mq</t>
+          <t>j32a3mqs</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
@@ -21879,7 +21884,7 @@
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>lUkw2EZ</t>
+          <t>lUkw2EZn</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
@@ -21889,7 +21894,7 @@
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>tjY4uUe</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
@@ -22169,7 +22174,7 @@
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>zFLwLRZ</t>
+          <t>zFLwLRZS</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
@@ -22179,7 +22184,7 @@
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>EJLKYOz</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
@@ -22459,7 +22464,7 @@
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>S8Ygn9M</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
@@ -22469,7 +22474,7 @@
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>tSiEeKv</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
@@ -22749,7 +22754,7 @@
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>619UPLr</t>
+          <t>619UPLrb</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
@@ -22759,7 +22764,7 @@
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>MVSS7qF</t>
+          <t>MVSS7qFe</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
@@ -23039,7 +23044,7 @@
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>n10g3Kf</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
@@ -23049,7 +23054,7 @@
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>bBhpZV2</t>
+          <t>bBhpZV2s</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
@@ -23329,7 +23334,7 @@
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>MLVBCoY</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
@@ -23339,7 +23344,7 @@
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>4IdjsvY</t>
+          <t>4IdjsvY2</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
@@ -23619,7 +23624,7 @@
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>xjigzK8</t>
+          <t>xjigzK81</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
@@ -23629,7 +23634,7 @@
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>Qu12kvX</t>
+          <t>Qu12kvXf</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
@@ -23909,7 +23914,7 @@
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>A72TGDl</t>
+          <t>A72TGDlt</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
@@ -23919,7 +23924,7 @@
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>KtGrCa5</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
@@ -24207,7 +24212,7 @@
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>rTrn0h4</t>
+          <t>rTrn0h4a</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
@@ -24217,7 +24222,7 @@
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>AcgUMf0</t>
+          <t>AcgUMf0E</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
@@ -24498,7 +24503,7 @@
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t>EJLKYOz</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="AZ83" t="inlineStr">
@@ -24508,7 +24513,7 @@
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>lUkw2EZ</t>
+          <t>lUkw2EZn</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
@@ -24789,7 +24794,7 @@
       </c>
       <c r="AY84" t="inlineStr">
         <is>
-          <t>EJLKYOz</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="AZ84" t="inlineStr">
@@ -24799,7 +24804,7 @@
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>tjY4uUe</t>
+          <t>tjY4uUem</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
@@ -25088,7 +25093,7 @@
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t>Qu12kvX</t>
+          <t>Qu12kvXf</t>
         </is>
       </c>
       <c r="AZ85" t="inlineStr">
@@ -25098,7 +25103,7 @@
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>lUkw2EZ</t>
+          <t>lUkw2EZn</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">

--- a/p6_deployment/data/italy/missing/data_understanding/all/df_match_miss.xlsx
+++ b/p6_deployment/data/italy/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH85"/>
+  <dimension ref="A1:BH101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24250,192 +24250,191 @@
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>Oj506F56</t>
+          <t>CMCRCR04</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>15.05.2024 16:00</t>
+          <t>01.04.2024 15:45</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Maresca F.
+          <t>Dionisi F.
  (Ita)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Stadio Olimpico
- (Rome)</t>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>70 634</t>
+          <t>80 018</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>70 634</t>
+          <t>71 551</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Juventus
-Winner</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>59%</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD83" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr">
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH83" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W83" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AA83" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AD83" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE83" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AF83" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AG83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI83" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AL83" t="inlineStr">
         <is>
           <t>2</t>
@@ -24443,54 +24442,54 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>568</t>
         </is>
       </c>
       <c r="AN83" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>372</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>517</t>
         </is>
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>316</t>
         </is>
       </c>
       <c r="AQ83" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AR83" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>96</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AV83" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AV83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AW83" t="inlineStr">
         <is>
           <t>111</t>
@@ -24498,37 +24497,37 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>111</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t>EJLKYOzb</t>
+          <t>j32a3mqs</t>
         </is>
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>gasperini gian piero</t>
+          <t>inzaghi simone</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>lUkw2EZn</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
         <is>
-          <t>allegri massimiliano</t>
+          <t>nicola davide</t>
         </is>
       </c>
       <c r="BC83" t="n">
         <v>77</v>
       </c>
       <c r="BD83" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="BE83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF83" t="inlineStr">
         <is>
@@ -24541,247 +24540,246 @@
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>KrUMD1Kd</t>
+          <t>KnGZA5VG</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>24.04.2024 16:00</t>
+          <t>01.04.2024 13:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>La Penna F.
+          <t>Marcenaro M.
  (Ita)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Gewiss Stadium
- (Bergamo)</t>
+          <t>Stadio Via del Mare
+ (Lecce)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>21 747</t>
+          <t>40 670</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>14 909</t>
+          <t>29 031</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>8C9JjMXu</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>Advancing to next round
-Atalanta</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>Fiorentina</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>2.11</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>0.59</t>
-        </is>
-      </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>57%</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>43%</t>
-        </is>
-      </c>
-      <c r="Q84" t="inlineStr">
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE84" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr">
+      <c r="AF84" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T84" t="inlineStr">
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="AN84" t="inlineStr">
+        <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="AP84" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="AQ84" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W84" t="inlineStr">
+      <c r="AV84" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE84" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AF84" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AG84" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI84" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL84" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>473</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>361</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>362</t>
-        </is>
-      </c>
-      <c r="AP84" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="AQ84" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="AS84" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="AT84" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AU84" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AV84" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AW84" t="inlineStr">
         <is>
           <t>112</t>
@@ -24789,344 +24787,4991 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
-          <t>EJLKYOzb</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>gasperini gian piero</t>
+          <t>gotti luca</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>tjY4uUem</t>
+          <t>xjigzK81</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
         <is>
-          <t>italiano vincenzo</t>
+          <t>de rossi daniele</t>
         </is>
       </c>
       <c r="BC84" t="n">
         <v>77</v>
       </c>
       <c r="BD84" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="BE84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF84" t="inlineStr">
         <is>
           <t>2023_2024</t>
         </is>
       </c>
-      <c r="BG84" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BH84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="BG84" t="inlineStr"/>
+      <c r="BH84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>dh7TdRoQ</t>
+          <t>hM5FFTGo</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>23.04.2024 16:00</t>
+          <t>01.04.2024 10:00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Orsato D.
+          <t>Doveri D.
  (Ita)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
+        <is>
+          <t>Unipol Domus
+ (Cagliari)</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>16 416</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>16 285</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD85" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE85" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AF85" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AG85" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL85" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="AN85" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="AP85" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="AQ85" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="AT85" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AV85" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>zFLwLRZS</t>
+        </is>
+      </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>ranieri claudio</t>
+        </is>
+      </c>
+      <c r="BA85" t="inlineStr">
+        <is>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+      <c r="BB85" t="inlineStr">
+        <is>
+          <t>baroni marco</t>
+        </is>
+      </c>
+      <c r="BC85" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD85" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF85" t="inlineStr">
+        <is>
+          <t>2023_2024</t>
+        </is>
+      </c>
+      <c r="BG85" t="inlineStr"/>
+      <c r="BH85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="inlineStr">
+        <is>
+          <t>GE9r9q0T</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>01.04.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Fabbri M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Mapei Stadium – Città del Tricolore
+ (Reggio Emilia)</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>21 525</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>11 512</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>QDdvI0zl</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Sassuolo</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD86" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL86" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>471</t>
+        </is>
+      </c>
+      <c r="AN86" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="AP86" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="AQ86" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="AT86" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AV86" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>AcgUMf0E</t>
+        </is>
+      </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>ballardini davide</t>
+        </is>
+      </c>
+      <c r="BA86" t="inlineStr">
+        <is>
+          <t>EDkXRoLT</t>
+        </is>
+      </c>
+      <c r="BB86" t="inlineStr">
+        <is>
+          <t>cioffi gabriele</t>
+        </is>
+      </c>
+      <c r="BC86" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD86" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF86" t="inlineStr">
+        <is>
+          <t>2023_2024</t>
+        </is>
+      </c>
+      <c r="BG86" t="inlineStr"/>
+      <c r="BH86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="inlineStr">
+        <is>
+          <t>vJHXjpvo</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>01.04.2024 07:30</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Feliciani E.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Stadio Renato Dall'Ara
+ (Bologna)</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>38 279</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>27 255</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Salernitana</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE87" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL87" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>774</t>
+        </is>
+      </c>
+      <c r="AN87" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>704</t>
+        </is>
+      </c>
+      <c r="AP87" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="AQ87" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="AT87" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AV87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>bBhpZV2s</t>
+        </is>
+      </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>motta thiago</t>
+        </is>
+      </c>
+      <c r="BA87" t="inlineStr">
+        <is>
+          <t>rTrn0h4a</t>
+        </is>
+      </c>
+      <c r="BB87" t="inlineStr">
+        <is>
+          <t>colantuono stefano</t>
+        </is>
+      </c>
+      <c r="BC87" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD87" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF87" t="inlineStr">
+        <is>
+          <t>2023_2024</t>
+        </is>
+      </c>
+      <c r="BG87" t="inlineStr"/>
+      <c r="BH87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="inlineStr">
+        <is>
+          <t>j7OIEmWi</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>30.03.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Maresca F.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Stadio Artemio Franchi
+ (Florence)</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>43 147</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>32 567</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD88" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE88" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF88" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AG88" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL88" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="AN88" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="AP88" t="inlineStr">
+        <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="AQ88" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="AT88" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AV88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>tjY4uUem</t>
+        </is>
+      </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>italiano vincenzo</t>
+        </is>
+      </c>
+      <c r="BA88" t="inlineStr">
+        <is>
+          <t>A72TGDlt</t>
+        </is>
+      </c>
+      <c r="BB88" t="inlineStr">
+        <is>
+          <t>pioli stefano</t>
+        </is>
+      </c>
+      <c r="BC88" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD88" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF88" t="inlineStr">
+        <is>
+          <t>2023_2024</t>
+        </is>
+      </c>
+      <c r="BG88" t="inlineStr"/>
+      <c r="BH88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>tdHVBoGA</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>30.03.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Colombo A.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
         <is>
           <t>Stadio Olimpico
  (Rome)</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>70 634</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>38 000</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>57 000</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
         <is>
           <t>URcSl02h</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t>Lazio</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="K89" t="inlineStr">
         <is>
           <t>C06aJvIB</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>Juventus
-Advancing to next round</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>0.53</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr">
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>0.58</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE89" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AF89" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL89" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="AN89" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="AP89" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="AQ89" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="AT89" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AV89" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>Qu12kvXf</t>
+        </is>
+      </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>tudor igor</t>
+        </is>
+      </c>
+      <c r="BA89" t="inlineStr">
+        <is>
+          <t>lUkw2EZn</t>
+        </is>
+      </c>
+      <c r="BB89" t="inlineStr">
+        <is>
+          <t>allegri massimiliano</t>
+        </is>
+      </c>
+      <c r="BC89" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD89" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF89" t="inlineStr">
+        <is>
+          <t>2023_2024</t>
+        </is>
+      </c>
+      <c r="BG89" t="inlineStr"/>
+      <c r="BH89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="inlineStr">
+        <is>
+          <t>YVDND7ob</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>30.03.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Sacchi J. L.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>36 599</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>31 462</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE90" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AF90" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AG90" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="AN90" t="inlineStr">
+        <is>
+          <t>425</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="AP90" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="AQ90" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AT90" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AV90" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>gilardino alberto</t>
+        </is>
+      </c>
+      <c r="BA90" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="BB90" t="inlineStr">
+        <is>
+          <t>di francesco eusebio</t>
+        </is>
+      </c>
+      <c r="BC90" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD90" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF90" t="inlineStr">
+        <is>
+          <t>2023_2024</t>
+        </is>
+      </c>
+      <c r="BG90" t="inlineStr"/>
+      <c r="BH90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="inlineStr">
+        <is>
+          <t>YgdA438p</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>30.03.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Aureliano G.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico di Torino
+ (Turin)</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>28 177</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>24 286</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD91" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE91" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AF91" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AG91" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL91" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>554</t>
+        </is>
+      </c>
+      <c r="AN91" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="AP91" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="AQ91" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="AT91" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AV91" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>4IdjsvY2</t>
+        </is>
+      </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>juric ivan</t>
+        </is>
+      </c>
+      <c r="BA91" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+      <c r="BB91" t="inlineStr">
+        <is>
+          <t>palladino raffaele</t>
+        </is>
+      </c>
+      <c r="BC91" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD91" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF91" t="inlineStr">
+        <is>
+          <t>2023_2024</t>
+        </is>
+      </c>
+      <c r="BG91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BH91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="inlineStr">
+        <is>
+          <t>2B5vAPpN</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>30.03.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Pairetto L.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Stadio Diego Armando Maradona
+ (Naples)</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>54 726</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>50 000</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD92" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AG92" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL92" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM92" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
+      <c r="AN92" t="inlineStr">
+        <is>
+          <t>383</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="AP92" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="AQ92" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="AT92" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AV92" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>MVSS7qFe</t>
+        </is>
+      </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>calzona francesco</t>
+        </is>
+      </c>
+      <c r="BA92" t="inlineStr">
+        <is>
+          <t>EJLKYOzb</t>
+        </is>
+      </c>
+      <c r="BB92" t="inlineStr">
+        <is>
+          <t>gasperini gian piero</t>
+        </is>
+      </c>
+      <c r="BC92" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD92" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF92" t="inlineStr">
+        <is>
+          <t>2023_2024</t>
+        </is>
+      </c>
+      <c r="BG92" t="inlineStr"/>
+      <c r="BH92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="inlineStr">
+        <is>
+          <t>C2pt1U1h</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>17.03.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>La Penna F.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>80 018</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>71 551</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AF93" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AG93" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM93" t="inlineStr">
+        <is>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="AN93" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="AP93" t="inlineStr">
+        <is>
+          <t>384</t>
+        </is>
+      </c>
+      <c r="AQ93" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AT93" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AV93" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>j32a3mqs</t>
+        </is>
+      </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>inzaghi simone</t>
+        </is>
+      </c>
+      <c r="BA93" t="inlineStr">
+        <is>
+          <t>MVSS7qFe</t>
+        </is>
+      </c>
+      <c r="BB93" t="inlineStr">
+        <is>
+          <t>calzona francesco</t>
+        </is>
+      </c>
+      <c r="BC93" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD93" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF93" t="inlineStr">
+        <is>
+          <t>2023_2024</t>
+        </is>
+      </c>
+      <c r="BG93" t="inlineStr"/>
+      <c r="BH93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>nLxgbSoB</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>17.03.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Manganiello G.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico
+ (Rome)</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>70 634</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>66 871</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>QDdvI0zl</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Sassuolo</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE94" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AF94" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AG94" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM94" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="AN94" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>552</t>
+        </is>
+      </c>
+      <c r="AP94" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="AQ94" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AT94" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AV94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>xjigzK81</t>
+        </is>
+      </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>de rossi daniele</t>
+        </is>
+      </c>
+      <c r="BA94" t="inlineStr">
+        <is>
+          <t>AcgUMf0E</t>
+        </is>
+      </c>
+      <c r="BB94" t="inlineStr">
+        <is>
+          <t>ballardini davide</t>
+        </is>
+      </c>
+      <c r="BC94" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD94" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF94" t="inlineStr">
+        <is>
+          <t>2023_2024</t>
+        </is>
+      </c>
+      <c r="BG94" t="inlineStr"/>
+      <c r="BH94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="inlineStr">
+        <is>
+          <t>xAV5eQVT</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>17.03.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Mariani M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Stadio Marc'Antonio Bentegodi
+ (Verona)</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>39 211</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>26 165</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD95" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AF95" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AG95" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL95" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM95" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="AN95" t="inlineStr">
+        <is>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="AP95" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="AQ95" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="AT95" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AV95" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>baroni marco</t>
+        </is>
+      </c>
+      <c r="BA95" t="inlineStr">
+        <is>
+          <t>A72TGDlt</t>
+        </is>
+      </c>
+      <c r="BB95" t="inlineStr">
+        <is>
+          <t>pioli stefano</t>
+        </is>
+      </c>
+      <c r="BC95" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD95" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF95" t="inlineStr">
+        <is>
+          <t>2023_2024</t>
+        </is>
+      </c>
+      <c r="BG95" t="inlineStr"/>
+      <c r="BH95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="inlineStr">
+        <is>
+          <t>jgqp0lHb</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>17.03.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Giua A.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Allianz Stadium
+ (Turin)</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>41 507</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>40 098</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>0.89</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE96" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AF96" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AG96" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM96" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="AN96" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>459</t>
+        </is>
+      </c>
+      <c r="AP96" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="AQ96" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AT96" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AV96" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>lUkw2EZn</t>
+        </is>
+      </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>allegri massimiliano</t>
+        </is>
+      </c>
+      <c r="BA96" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="BB96" t="inlineStr">
+        <is>
+          <t>gilardino alberto</t>
+        </is>
+      </c>
+      <c r="BC96" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD96" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF96" t="inlineStr">
+        <is>
+          <t>2023_2024</t>
+        </is>
+      </c>
+      <c r="BG96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BH96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="inlineStr">
+        <is>
+          <t>4xox2Ann</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>16.03.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Rapuano A.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Stadio Benito Stirpe
+ (Frosinone)</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>16 227</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>15 780</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>3.26</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
         <is>
           <t>57%</t>
         </is>
       </c>
-      <c r="P85" t="inlineStr">
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD97" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL97" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="AN97" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="AP97" t="inlineStr">
+        <is>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="AQ97" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="AT97" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AV97" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>n10g3KfJ</t>
+        </is>
+      </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>di francesco eusebio</t>
+        </is>
+      </c>
+      <c r="BA97" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="BB97" t="inlineStr">
+        <is>
+          <t>martusciello giovanni</t>
+        </is>
+      </c>
+      <c r="BC97" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD97" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF97" t="inlineStr">
+        <is>
+          <t>2023_2024</t>
+        </is>
+      </c>
+      <c r="BG97" t="inlineStr"/>
+      <c r="BH97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>trxccn1H</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>16.03.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Maresca F.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Stadio Arechi
+ (Salerno)</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>37 800</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>15 376</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Salernitana</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF98" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL98" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM98" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="AN98" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="AP98" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="AQ98" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="AT98" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AV98" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>UqSpIhMs</t>
+        </is>
+      </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>liverani fabio</t>
+        </is>
+      </c>
+      <c r="BA98" t="inlineStr">
+        <is>
+          <t>KtGrCa5d</t>
+        </is>
+      </c>
+      <c r="BB98" t="inlineStr">
+        <is>
+          <t>gotti luca</t>
+        </is>
+      </c>
+      <c r="BC98" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD98" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF98" t="inlineStr">
+        <is>
+          <t>2023_2024</t>
+        </is>
+      </c>
+      <c r="BG98" t="inlineStr"/>
+      <c r="BH98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>YHYla8W4</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>16.03.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Marcenaro M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Brianteo
+ (Monza)</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>16 917</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>14 145</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AF99" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>536</t>
+        </is>
+      </c>
+      <c r="AN99" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>467</t>
+        </is>
+      </c>
+      <c r="AP99" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="AQ99" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="AT99" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AV99" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>619UPLrb</t>
+        </is>
+      </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>palladino raffaele</t>
+        </is>
+      </c>
+      <c r="BA99" t="inlineStr">
+        <is>
+          <t>zFLwLRZS</t>
+        </is>
+      </c>
+      <c r="BB99" t="inlineStr">
+        <is>
+          <t>ranieri claudio</t>
+        </is>
+      </c>
+      <c r="BC99" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD99" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF99" t="inlineStr">
+        <is>
+          <t>2023_2024</t>
+        </is>
+      </c>
+      <c r="BG99" t="inlineStr"/>
+      <c r="BH99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>KYz1d6GN</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>16.03.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Colombo A.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Bluenergy Stadium - Stadio Friuli
+ (Udine)</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>25 144</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>21 223</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
         <is>
           <t>43%</t>
         </is>
       </c>
-      <c r="Q85" t="inlineStr">
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE100" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AF100" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AG100" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL100" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="AN100" t="inlineStr">
+        <is>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="AP100" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="AQ100" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AT100" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AV100" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>EDkXRoLT</t>
+        </is>
+      </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>cioffi gabriele</t>
+        </is>
+      </c>
+      <c r="BA100" t="inlineStr">
+        <is>
+          <t>4IdjsvY2</t>
+        </is>
+      </c>
+      <c r="BB100" t="inlineStr">
+        <is>
+          <t>juric ivan</t>
+        </is>
+      </c>
+      <c r="BC100" t="n">
+        <v>77</v>
+      </c>
+      <c r="BD100" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF100" t="inlineStr">
+        <is>
+          <t>2023_2024</t>
+        </is>
+      </c>
+      <c r="BG100" t="inlineStr"/>
+      <c r="BH100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>QonY2jXu</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>15.03.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Fabbri M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Stadio Carlo Castellani
+ (Empoli)</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>16 284</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>11 185</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Empoli</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="R85" t="inlineStr">
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AF101" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AG101" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W85" t="inlineStr">
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="X85" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE85" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AF85" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AG85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>467</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>564</t>
-        </is>
-      </c>
-      <c r="AP85" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
-      </c>
-      <c r="AQ85" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="AS85" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="AT85" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="AU85" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AV85" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AW85" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="AX85" t="inlineStr">
+      <c r="AL101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="AN101" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="AP101" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="AQ101" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="AT101" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AV101" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
         <is>
           <t>113</t>
         </is>
       </c>
-      <c r="AY85" t="inlineStr">
-        <is>
-          <t>Qu12kvXf</t>
-        </is>
-      </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>tudor igor</t>
-        </is>
-      </c>
-      <c r="BA85" t="inlineStr">
-        <is>
-          <t>lUkw2EZn</t>
-        </is>
-      </c>
-      <c r="BB85" t="inlineStr">
-        <is>
-          <t>allegri massimiliano</t>
-        </is>
-      </c>
-      <c r="BC85" t="n">
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>nicola davide</t>
+        </is>
+      </c>
+      <c r="BA101" t="inlineStr">
+        <is>
+          <t>bBhpZV2s</t>
+        </is>
+      </c>
+      <c r="BB101" t="inlineStr">
+        <is>
+          <t>motta thiago</t>
+        </is>
+      </c>
+      <c r="BC101" t="n">
         <v>77</v>
       </c>
-      <c r="BD85" t="n">
-        <v>773</v>
-      </c>
-      <c r="BE85" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF85" t="inlineStr">
+      <c r="BD101" t="n">
+        <v>771</v>
+      </c>
+      <c r="BE101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF101" t="inlineStr">
         <is>
           <t>2023_2024</t>
         </is>
       </c>
-      <c r="BG85" t="inlineStr"/>
-      <c r="BH85" t="inlineStr"/>
+      <c r="BG101" t="inlineStr"/>
+      <c r="BH101" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
